--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-practitioner.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:09:55+00:00</t>
+    <t>2026-08-20T16:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-practitioner.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:34:37+00:00</t>
+    <t>2026-08-21T09:28:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-practitioner.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-practitioner.xlsx
@@ -39,7 +39,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>RORPractitionerProfile</t>
+    <t>RORPractitioner</t>
   </si>
   <si>
     <t>Title</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T09:28:33+00:00</t>
+    <t>2026-08-21T09:39:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-practitioner.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:30:36+00:00</t>
+    <t>2026-08-21T16:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3075,10 +3075,10 @@
     <t>Practitioner.qualification:savoirFaire.issuer</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorSpecialty</t>
-  </si>
-  <si>
-    <t>rorSpecialty</t>
+    <t>Practitioner.qualification:savoirFaire/rorSpecialty</t>
+  </si>
+  <si>
+    <t>savoirFaire/rorSpecialty</t>
   </si>
   <si>
     <t>specialite (SavoirFaire) : Spécialité ordinale</t>
@@ -3087,34 +3087,34 @@
     <t>SavoirFaire.specialite</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorSpecialty.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSpecialty.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSpecialty.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSpecialty.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSpecialty.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSpecialty.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSpecialty.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSpecialty.code.coding</t>
+    <t>Practitioner.qualification:savoirFaire/rorSpecialty.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSpecialty.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSpecialty.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSpecialty.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSpecialty.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSpecialty.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSpecialty.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSpecialty.code.coding</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorSpecialty.code.coding:typeSavoirFaire</t>
+    <t>Practitioner.qualification:savoirFaire/rorSpecialty.code.coding:typeSavoirFaire</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -3123,7 +3123,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorSpecialty.code.coding:valeur</t>
+    <t>Practitioner.qualification:savoirFaire/rorSpecialty.code.coding:valeur</t>
   </si>
   <si>
     <t>valeur</t>
@@ -3132,19 +3132,19 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J210-SpecialiteOrdinale-ROR/FHIR/JDV-J210-SpecialiteOrdinale-ROR</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorSpecialty.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSpecialty.period</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSpecialty.issuer</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorCompetence</t>
-  </si>
-  <si>
-    <t>rorCompetence</t>
+    <t>Practitioner.qualification:savoirFaire/rorSpecialty.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSpecialty.period</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSpecialty.issuer</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorCompetence</t>
+  </si>
+  <si>
+    <t>savoirFaire/rorCompetence</t>
   </si>
   <si>
     <t>competence (SavoirFaire) : Compétence acquise par le professionnel</t>
@@ -3153,31 +3153,31 @@
     <t>SavoirFaire.competence</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorCompetence.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorCompetence.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorCompetence.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorCompetence.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorCompetence.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorCompetence.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorCompetence.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorCompetence.code.coding</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorCompetence.code.coding:typeSavoirFaire</t>
+    <t>Practitioner.qualification:savoirFaire/rorCompetence.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorCompetence.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorCompetence.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorCompetence.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorCompetence.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorCompetence.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorCompetence.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorCompetence.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorCompetence.code.coding:typeSavoirFaire</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -3186,25 +3186,25 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorCompetence.code.coding:valeur</t>
+    <t>Practitioner.qualification:savoirFaire/rorCompetence.code.coding:valeur</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J232-Competence-ROR/FHIR/JDV-J232-Competence-ROR</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorCompetence.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorCompetence.period</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorCompetence.issuer</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExclusiveCompetence</t>
-  </si>
-  <si>
-    <t>rorExclusiveCompetence</t>
+    <t>Practitioner.qualification:savoirFaire/rorCompetence.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorCompetence.period</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorCompetence.issuer</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExclusiveCompetence</t>
+  </si>
+  <si>
+    <t>savoirFaire/rorExclusiveCompetence</t>
   </si>
   <si>
     <t>competenceExclusive (SavoirFaire) : Compétence exclusive</t>
@@ -3213,31 +3213,31 @@
     <t>SavoirFaire.competenceExclusive</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorExclusiveCompetence.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExclusiveCompetence.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExclusiveCompetence.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExclusiveCompetence.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExclusiveCompetence.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExclusiveCompetence.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExclusiveCompetence.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExclusiveCompetence.code.coding</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExclusiveCompetence.code.coding:typeSavoirFaire</t>
+    <t>Practitioner.qualification:savoirFaire/rorExclusiveCompetence.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExclusiveCompetence.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExclusiveCompetence.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExclusiveCompetence.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExclusiveCompetence.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExclusiveCompetence.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExclusiveCompetence.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExclusiveCompetence.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExclusiveCompetence.code.coding:typeSavoirFaire</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -3246,25 +3246,25 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorExclusiveCompetence.code.coding:valeur</t>
+    <t>Practitioner.qualification:savoirFaire/rorExclusiveCompetence.code.coding:valeur</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J211-CompetenceExclusive-ROR/FHIR/JDV-J211-CompetenceExclusive-ROR</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorExclusiveCompetence.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExclusiveCompetence.period</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExclusiveCompetence.issuer</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSpecificOrientation</t>
-  </si>
-  <si>
-    <t>rorSpecificOrientation</t>
+    <t>Practitioner.qualification:savoirFaire/rorExclusiveCompetence.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExclusiveCompetence.period</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExclusiveCompetence.issuer</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSpecificOrientation</t>
+  </si>
+  <si>
+    <t>savoirFaire/rorSpecificOrientation</t>
   </si>
   <si>
     <t>orientationParticuliere (SavoirFaire) : Orientation particulière</t>
@@ -3273,31 +3273,31 @@
     <t>SavoirFaire.orientationParticuliere</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorSpecificOrientation.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSpecificOrientation.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSpecificOrientation.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSpecificOrientation.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSpecificOrientation.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSpecificOrientation.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSpecificOrientation.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSpecificOrientation.code.coding</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSpecificOrientation.code.coding:typeSavoirFaire</t>
+    <t>Practitioner.qualification:savoirFaire/rorSpecificOrientation.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSpecificOrientation.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSpecificOrientation.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSpecificOrientation.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSpecificOrientation.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSpecificOrientation.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSpecificOrientation.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSpecificOrientation.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSpecificOrientation.code.coding:typeSavoirFaire</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -3306,25 +3306,25 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorSpecificOrientation.code.coding:valeur</t>
+    <t>Practitioner.qualification:savoirFaire/rorSpecificOrientation.code.coding:valeur</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J212-OrientationParticuliere-ROR/FHIR/JDV-J212-OrientationParticuliere-ROR</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorSpecificOrientation.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSpecificOrientation.period</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSpecificOrientation.issuer</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExpertiseCapacity</t>
-  </si>
-  <si>
-    <t>rorExpertiseCapacity</t>
+    <t>Practitioner.qualification:savoirFaire/rorSpecificOrientation.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSpecificOrientation.period</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSpecificOrientation.issuer</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExpertiseCapacity</t>
+  </si>
+  <si>
+    <t>savoirFaire/rorExpertiseCapacity</t>
   </si>
   <si>
     <t>capacite (SavoirFaire) : Capacité de médecine</t>
@@ -3333,31 +3333,31 @@
     <t>SavoirFaire.capacite</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorExpertiseCapacity.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExpertiseCapacity.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExpertiseCapacity.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExpertiseCapacity.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExpertiseCapacity.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExpertiseCapacity.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExpertiseCapacity.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExpertiseCapacity.code.coding</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExpertiseCapacity.code.coding:typeSavoirFaire</t>
+    <t>Practitioner.qualification:savoirFaire/rorExpertiseCapacity.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExpertiseCapacity.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExpertiseCapacity.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExpertiseCapacity.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExpertiseCapacity.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExpertiseCapacity.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExpertiseCapacity.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExpertiseCapacity.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExpertiseCapacity.code.coding:typeSavoirFaire</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -3366,25 +3366,25 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorExpertiseCapacity.code.coding:valeur</t>
+    <t>Practitioner.qualification:savoirFaire/rorExpertiseCapacity.code.coding:valeur</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J213-CapaciteSavoirFaire-ROR/FHIR/JDV-J213-CapaciteSavoirFaire-ROR</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorExpertiseCapacity.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExpertiseCapacity.period</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorExpertiseCapacity.issuer</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorQualificationPAC</t>
-  </si>
-  <si>
-    <t>rorQualificationPAC</t>
+    <t>Practitioner.qualification:savoirFaire/rorExpertiseCapacity.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExpertiseCapacity.period</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorExpertiseCapacity.issuer</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorQualificationPAC</t>
+  </si>
+  <si>
+    <t>savoirFaire/rorQualificationPAC</t>
   </si>
   <si>
     <t>qualificationPAC (SavoirFaire) : Qualification de praticien adjoint contractuel</t>
@@ -3393,31 +3393,31 @@
     <t>SavoirFaire.qualificationPAC</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorQualificationPAC.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorQualificationPAC.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorQualificationPAC.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorQualificationPAC.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorQualificationPAC.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorQualificationPAC.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorQualificationPAC.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorQualificationPAC.code.coding</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorQualificationPAC.code.coding:typeSavoirFaire</t>
+    <t>Practitioner.qualification:savoirFaire/rorQualificationPAC.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorQualificationPAC.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorQualificationPAC.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorQualificationPAC.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorQualificationPAC.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorQualificationPAC.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorQualificationPAC.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorQualificationPAC.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorQualificationPAC.code.coding:typeSavoirFaire</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -3426,25 +3426,25 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorQualificationPAC.code.coding:valeur</t>
+    <t>Practitioner.qualification:savoirFaire/rorQualificationPAC.code.coding:valeur</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J214-QualificationPAC-ROR/FHIR/JDV-J214-QualificationPAC-ROR</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorQualificationPAC.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorQualificationPAC.period</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorQualificationPAC.issuer</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorNonQualifyingDESC</t>
-  </si>
-  <si>
-    <t>rorNonQualifyingDESC</t>
+    <t>Practitioner.qualification:savoirFaire/rorQualificationPAC.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorQualificationPAC.period</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorQualificationPAC.issuer</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorNonQualifyingDESC</t>
+  </si>
+  <si>
+    <t>savoirFaire/rorNonQualifyingDESC</t>
   </si>
   <si>
     <t>DESCNonQualifiant (SavoirFaire) : Diplôme d'études spécialisées complémentaires (DESC)</t>
@@ -3453,31 +3453,31 @@
     <t>SavoirFaire.DESCNonQualifiant</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorNonQualifyingDESC.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorNonQualifyingDESC.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorNonQualifyingDESC.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorNonQualifyingDESC.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorNonQualifyingDESC.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorNonQualifyingDESC.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorNonQualifyingDESC.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorNonQualifyingDESC.code.coding</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorNonQualifyingDESC.code.coding:typeSavoirFaire</t>
+    <t>Practitioner.qualification:savoirFaire/rorNonQualifyingDESC.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorNonQualifyingDESC.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorNonQualifyingDESC.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorNonQualifyingDESC.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorNonQualifyingDESC.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorNonQualifyingDESC.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorNonQualifyingDESC.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorNonQualifyingDESC.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorNonQualifyingDESC.code.coding:typeSavoirFaire</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -3486,25 +3486,25 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorNonQualifyingDESC.code.coding:valeur</t>
+    <t>Practitioner.qualification:savoirFaire/rorNonQualifyingDESC.code.coding:valeur</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J215-DESCnonQualifiant-ROR/FHIR/JDV-J215-DESCnonQualifiant-ROR</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorNonQualifyingDESC.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorNonQualifyingDESC.period</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorNonQualifyingDESC.issuer</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSupplementaryExerciseRight</t>
-  </si>
-  <si>
-    <t>rorSupplementaryExerciseRight</t>
+    <t>Practitioner.qualification:savoirFaire/rorNonQualifyingDESC.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorNonQualifyingDESC.period</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorNonQualifyingDESC.issuer</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSupplementaryExerciseRight</t>
+  </si>
+  <si>
+    <t>savoirFaire/rorSupplementaryExerciseRight</t>
   </si>
   <si>
     <t>droitExerciceComplémentaire (SavoirFaire) : Droit d'exercice complémentaire du professionnel</t>
@@ -3513,31 +3513,31 @@
     <t>SavoirFaire.droitExerciceComplémentaire</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorSupplementaryExerciseRight.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSupplementaryExerciseRight.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSupplementaryExerciseRight.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSupplementaryExerciseRight.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSupplementaryExerciseRight.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSupplementaryExerciseRight.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSupplementaryExerciseRight.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSupplementaryExerciseRight.code.coding</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSupplementaryExerciseRight.code.coding:typeSavoirFaire</t>
+    <t>Practitioner.qualification:savoirFaire/rorSupplementaryExerciseRight.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSupplementaryExerciseRight.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSupplementaryExerciseRight.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSupplementaryExerciseRight.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSupplementaryExerciseRight.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSupplementaryExerciseRight.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSupplementaryExerciseRight.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSupplementaryExerciseRight.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSupplementaryExerciseRight.code.coding:typeSavoirFaire</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -3546,19 +3546,19 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorSupplementaryExerciseRight.code.coding:valeur</t>
+    <t>Practitioner.qualification:savoirFaire/rorSupplementaryExerciseRight.code.coding:valeur</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J216-DroitExerciceCompl-ROR/FHIR/JDV-J216-DroitExerciceCompl-ROR</t>
   </si>
   <si>
-    <t>Practitioner.qualification:rorSupplementaryExerciseRight.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSupplementaryExerciseRight.period</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:rorSupplementaryExerciseRight.issuer</t>
+    <t>Practitioner.qualification:savoirFaire/rorSupplementaryExerciseRight.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSupplementaryExerciseRight.period</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire/rorSupplementaryExerciseRight.issuer</t>
   </si>
   <si>
     <t>Practitioner.communication</t>
@@ -3909,7 +3909,7 @@
   <cols>
     <col min="1" max="1" width="82.7265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.71875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="29.5703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="35.15625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -44139,14 +44139,14 @@
         <v>84</v>
       </c>
       <c r="AB293" t="s" s="2">
-        <v>436</v>
+        <v>157</v>
       </c>
       <c r="AC293" s="2"/>
       <c r="AD293" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE293" t="s" s="2">
-        <v>131</v>
+        <v>890</v>
       </c>
       <c r="AF293" t="s" s="2">
         <v>891</v>
@@ -46073,14 +46073,14 @@
         <v>84</v>
       </c>
       <c r="AB307" t="s" s="2">
-        <v>436</v>
+        <v>157</v>
       </c>
       <c r="AC307" s="2"/>
       <c r="AD307" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE307" t="s" s="2">
-        <v>131</v>
+        <v>890</v>
       </c>
       <c r="AF307" t="s" s="2">
         <v>891</v>
@@ -48007,14 +48007,14 @@
         <v>84</v>
       </c>
       <c r="AB321" t="s" s="2">
-        <v>436</v>
+        <v>157</v>
       </c>
       <c r="AC321" s="2"/>
       <c r="AD321" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE321" t="s" s="2">
-        <v>131</v>
+        <v>890</v>
       </c>
       <c r="AF321" t="s" s="2">
         <v>891</v>
@@ -49941,14 +49941,14 @@
         <v>84</v>
       </c>
       <c r="AB335" t="s" s="2">
-        <v>436</v>
+        <v>157</v>
       </c>
       <c r="AC335" s="2"/>
       <c r="AD335" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE335" t="s" s="2">
-        <v>131</v>
+        <v>890</v>
       </c>
       <c r="AF335" t="s" s="2">
         <v>891</v>
@@ -51875,14 +51875,14 @@
         <v>84</v>
       </c>
       <c r="AB349" t="s" s="2">
-        <v>436</v>
+        <v>157</v>
       </c>
       <c r="AC349" s="2"/>
       <c r="AD349" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE349" t="s" s="2">
-        <v>131</v>
+        <v>890</v>
       </c>
       <c r="AF349" t="s" s="2">
         <v>891</v>
@@ -53809,14 +53809,14 @@
         <v>84</v>
       </c>
       <c r="AB363" t="s" s="2">
-        <v>436</v>
+        <v>157</v>
       </c>
       <c r="AC363" s="2"/>
       <c r="AD363" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE363" t="s" s="2">
-        <v>131</v>
+        <v>890</v>
       </c>
       <c r="AF363" t="s" s="2">
         <v>891</v>
@@ -55743,14 +55743,14 @@
         <v>84</v>
       </c>
       <c r="AB377" t="s" s="2">
-        <v>436</v>
+        <v>157</v>
       </c>
       <c r="AC377" s="2"/>
       <c r="AD377" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE377" t="s" s="2">
-        <v>131</v>
+        <v>890</v>
       </c>
       <c r="AF377" t="s" s="2">
         <v>891</v>
@@ -57677,14 +57677,14 @@
         <v>84</v>
       </c>
       <c r="AB391" t="s" s="2">
-        <v>436</v>
+        <v>157</v>
       </c>
       <c r="AC391" s="2"/>
       <c r="AD391" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE391" t="s" s="2">
-        <v>131</v>
+        <v>890</v>
       </c>
       <c r="AF391" t="s" s="2">
         <v>891</v>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-practitioner.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:03:39+00:00</t>
+    <t>2026-08-26T13:04:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
